--- a/Data/dim_employee.xlsx
+++ b/Data/dim_employee.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Machine Learning\Power BI\Projects\2\Dataset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analysis\Power BI\Projects\2- Sysco\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419662FC-D557-4C21-B312-E472BB1194AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF8AD26-D302-4723-83B6-B74118E70FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56350C31-280B-463A-A3AA-DD87B752F566}"/>
   </bookViews>
@@ -41,57 +41,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="89">
   <si>
-    <t>Employee Key</t>
-  </si>
-  <si>
-    <t>Full Name</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Title of Courtesy</t>
-  </si>
-  <si>
-    <t>Birth Date</t>
-  </si>
-  <si>
-    <t>Hire Date</t>
-  </si>
-  <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t>Postal Code</t>
-  </si>
-  <si>
-    <t>Country</t>
-  </si>
-  <si>
-    <t>Home Phone</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>Photo</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Reprts To</t>
-  </si>
-  <si>
-    <t>Photo Path</t>
-  </si>
-  <si>
     <t>Nancy Davolio</t>
   </si>
   <si>
@@ -306,6 +255,57 @@
   </si>
   <si>
     <t>Anne has a BA degree in English from St. Lawrence College.  She is fluent in French and German.</t>
+  </si>
+  <si>
+    <t>employee_key</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>title_of_courtesy</t>
+  </si>
+  <si>
+    <t>birth_date</t>
+  </si>
+  <si>
+    <t>hire_date</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t>postal_code</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>home_phone</t>
+  </si>
+  <si>
+    <t>extension</t>
+  </si>
+  <si>
+    <t>photo</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>reports_to</t>
+  </si>
+  <si>
+    <t>photo_path</t>
+  </si>
+  <si>
+    <t>full_name</t>
   </si>
 </sst>
 </file>
@@ -691,55 +691,55 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -747,52 +747,52 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>2</v>
+      </c>
+      <c r="D2" s="3">
+        <v>17875</v>
       </c>
       <c r="E2" s="3">
-        <v>17875</v>
-      </c>
-      <c r="F2" s="3">
         <v>33725</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="G2" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="2">
+        <v>8</v>
+      </c>
+      <c r="L2" s="2">
         <v>5467</v>
       </c>
+      <c r="M2" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="N2" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -800,52 +800,52 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="D3" s="3">
+        <v>19043</v>
       </c>
       <c r="E3" s="3">
-        <v>19043</v>
-      </c>
-      <c r="F3" s="3">
         <v>33830</v>
       </c>
+      <c r="F3" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="G3" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M3" s="2">
+        <v>19</v>
+      </c>
+      <c r="L3" s="2">
         <v>3457</v>
       </c>
+      <c r="M3" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="N3" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -853,52 +853,52 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>19</v>
+        <v>2</v>
+      </c>
+      <c r="D4" s="3">
+        <v>23253</v>
       </c>
       <c r="E4" s="3">
-        <v>23253</v>
-      </c>
-      <c r="F4" s="3">
         <v>33695</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="G4" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="2">
+        <v>3355</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q4" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M4" s="2">
-        <v>3355</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -906,52 +906,52 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>48</v>
+        <v>31</v>
+      </c>
+      <c r="D5" s="3">
+        <v>13777</v>
       </c>
       <c r="E5" s="3">
-        <v>13777</v>
-      </c>
-      <c r="F5" s="3">
         <v>34092</v>
       </c>
+      <c r="F5" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="G5" s="1" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="M5" s="2">
+        <v>35</v>
+      </c>
+      <c r="L5" s="2">
         <v>5176</v>
       </c>
+      <c r="M5" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="N5" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -959,52 +959,52 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>57</v>
+        <v>40</v>
+      </c>
+      <c r="D6" s="3">
+        <v>20152</v>
       </c>
       <c r="E6" s="3">
-        <v>20152</v>
-      </c>
-      <c r="F6" s="3">
         <v>34259</v>
       </c>
+      <c r="F6" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="G6" s="1" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="M6" s="2">
+        <v>46</v>
+      </c>
+      <c r="L6" s="2">
         <v>3453</v>
       </c>
+      <c r="M6" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="N6" s="1" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -1012,52 +1012,52 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>57</v>
+        <v>40</v>
+      </c>
+      <c r="D7" s="3">
+        <v>23194</v>
       </c>
       <c r="E7" s="3">
-        <v>23194</v>
-      </c>
-      <c r="F7" s="3">
         <v>34259</v>
       </c>
+      <c r="F7" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="G7" s="1" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="M7" s="2">
+        <v>52</v>
+      </c>
+      <c r="L7" s="2">
         <v>428</v>
       </c>
+      <c r="M7" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="N7" s="1" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -1065,52 +1065,52 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="3">
+        <v>22065</v>
+      </c>
+      <c r="E8" s="3">
+        <v>34336</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="3">
-        <v>22065</v>
-      </c>
-      <c r="F8" s="3">
-        <v>34336</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="L8" s="2">
+        <v>465</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="M8" s="2">
-        <v>465</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="O8" s="1" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -1118,52 +1118,52 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>19</v>
+        <v>2</v>
+      </c>
+      <c r="D9" s="3">
+        <v>21194</v>
       </c>
       <c r="E9" s="3">
-        <v>21194</v>
-      </c>
-      <c r="F9" s="3">
         <v>34398</v>
       </c>
+      <c r="F9" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="G9" s="1" t="s">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="M9" s="2">
+        <v>65</v>
+      </c>
+      <c r="L9" s="2">
         <v>2344</v>
       </c>
+      <c r="M9" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="N9" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -1171,52 +1171,52 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>19</v>
+        <v>2</v>
+      </c>
+      <c r="D10" s="3">
+        <v>24134</v>
       </c>
       <c r="E10" s="3">
-        <v>24134</v>
-      </c>
-      <c r="F10" s="3">
         <v>34653</v>
       </c>
+      <c r="F10" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="G10" s="1" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="M10" s="2">
+        <v>70</v>
+      </c>
+      <c r="L10" s="2">
         <v>452</v>
       </c>
+      <c r="M10" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="N10" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
